--- a/public/samples/bb-templates/BB-Template-Import-aep-vii.xlsx
+++ b/public/samples/bb-templates/BB-Template-Import-aep-vii.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -444,6 +444,9 @@
       <c r="M1" t="str">
         <v>detect_keys</v>
       </c>
+      <c r="N1" t="str">
+        <v>auto_discover_tabs</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -459,7 +462,7 @@
         <v>BB</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -485,10 +488,13 @@
       <c r="M2" t="str">
         <v/>
       </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -531,7 +537,7 @@
         <v>BB</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>1</v>

--- a/public/samples/bb-templates/BB-Template-Import-aep-vii.xlsx
+++ b/public/samples/bb-templates/BB-Template-Import-aep-vii.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView activeTab="2" tabRatio="500"/>
+  </bookViews>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Tabs" sheetId="2" r:id="rId2"/>
-    <sheet name="Groups" sheetId="3" r:id="rId3"/>
-    <sheet name="Columns" sheetId="4" r:id="rId4"/>
-    <sheet name="Legend" sheetId="5" r:id="rId5"/>
-    <sheet name="Notes" sheetId="6" r:id="rId6"/>
+    <sheet r:id="rId1" name="Template" sheetId="1"/>
+    <sheet r:id="rId2" name="Tabs" sheetId="2"/>
+    <sheet r:id="rId3" name="Groups" sheetId="3"/>
+    <sheet r:id="rId4" name="Columns" sheetId="4"/>
+    <sheet r:id="rId5" name="Legend" sheetId="5"/>
+    <sheet r:id="rId6" name="Notes" sheetId="6"/>
   </sheets>
+  <calcPr calcId="0" iterate="1" iterateCount="1000" iterateDelta="0.01"/>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -35,17 +39,218 @@
 </metadata>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+  <si>
+    <t>template_slug</t>
+  </si>
+  <si>
+    <t>agent_bank</t>
+  </si>
+  <si>
+    <t>template_class</t>
+  </si>
+  <si>
+    <t>sheet_name</t>
+  </si>
+  <si>
+    <t>header_row_index</t>
+  </si>
+  <si>
+    <t>header_row_span</t>
+  </si>
+  <si>
+    <t>auto_learned</t>
+  </si>
+  <si>
+    <t>tranche_count</t>
+  </si>
+  <si>
+    <t>has_grouping_rows</t>
+  </si>
+  <si>
+    <t>has_color_flags</t>
+  </si>
+  <si>
+    <t>summary_rows_above_header</t>
+  </si>
+  <si>
+    <t>summary_row_range</t>
+  </si>
+  <si>
+    <t>detect_keys</t>
+  </si>
+  <si>
+    <t>auto_discover_tabs</t>
+  </si>
+  <si>
+    <t>aep-vii</t>
+  </si>
+  <si>
+    <t>JP Morgan</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>3-9</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>tab_role</t>
+  </si>
+  <si>
+    <t>tab_sort</t>
+  </si>
+  <si>
+    <t>skip_row_keywords</t>
+  </si>
+  <si>
+    <t>expected_source_headers_json</t>
+  </si>
+  <si>
+    <t>LP_GRID</t>
+  </si>
+  <si>
+    <t>Total,Subtotal,Sub-Total,Grand Total,Sum,Net Total</t>
+  </si>
+  <si>
+    <t>["Investor","Moody's","S&amp;P","Net Worth","Total Commitment","Funded Commitment","Unfunded Commitment","% Total Unfunded Commitment","Concentration Limit","Excess Concentration","Eligible Unfunded Commitment","Advance Rate"]</t>
+  </si>
+  <si>
+    <t>group_sort</t>
+  </si>
+  <si>
+    <t>header_text</t>
+  </si>
+  <si>
+    <t>classification</t>
+  </si>
+  <si>
+    <t>Rated Included Investors</t>
+  </si>
+  <si>
+    <t>Rated Included</t>
+  </si>
+  <si>
+    <t>Non-Rated Included Investors</t>
+  </si>
+  <si>
+    <t>Non-Rated Included</t>
+  </si>
+  <si>
+    <t>Designated Investors</t>
+  </si>
+  <si>
+    <t>Designated Institutional</t>
+  </si>
+  <si>
+    <t>Excluded Investors</t>
+  </si>
+  <si>
+    <t>Ineligible Investors</t>
+  </si>
+  <si>
+    <t>column_sort</t>
+  </si>
+  <si>
+    <t>source_header</t>
+  </si>
+  <si>
+    <t>Investor</t>
+  </si>
+  <si>
+    <t>Moody's</t>
+  </si>
+  <si>
+    <t>S&amp;P</t>
+  </si>
+  <si>
+    <t>Net Worth</t>
+  </si>
+  <si>
+    <t>Total Commitment</t>
+  </si>
+  <si>
+    <t>Funded Commitment</t>
+  </si>
+  <si>
+    <t>Unfunded Commitment</t>
+  </si>
+  <si>
+    <t>% Total Unfunded Commitment</t>
+  </si>
+  <si>
+    <t>Concentration Limit</t>
+  </si>
+  <si>
+    <t>Excess Concentration</t>
+  </si>
+  <si>
+    <t>Eligible Unfunded Commitment</t>
+  </si>
+  <si>
+    <t>Advance Rate</t>
+  </si>
+  <si>
+    <t>legend_sort</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>meaning</t>
+  </si>
+  <si>
+    <t>Green shading</t>
+  </si>
+  <si>
+    <t>LP new to the BB, NOT via LP Transfer</t>
+  </si>
+  <si>
+    <t>Yellow shading</t>
+  </si>
+  <si>
+    <t>LP new to the BB via LP Transfer</t>
+  </si>
+  <si>
+    <t>Blue text</t>
+  </si>
+  <si>
+    <t>LP with a change in Commitment Amount</t>
+  </si>
+  <si>
+    <t>Underlined text</t>
+  </si>
+  <si>
+    <t>LP with a change in Category</t>
+  </si>
+  <si>
+    <t>note_sort</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>Cell formatting encodes LP-level deltas — capture during extraction, not just the cell value.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1">
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -66,18 +271,41 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+  <bag type="DXFComplements" extRef="DXFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -225,16 +453,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -356,110 +588,72 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E1732B45-76A7-47CE-8568-0B1E30AE2CCF}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="15" defaultColWidth="7.75390625" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>template_slug</v>
-      </c>
-      <c r="B1" t="str">
-        <v>agent_bank</v>
-      </c>
-      <c r="C1" t="str">
-        <v>template_class</v>
-      </c>
-      <c r="D1" t="str">
-        <v>sheet_name</v>
-      </c>
-      <c r="E1" t="str">
-        <v>header_row_index</v>
-      </c>
-      <c r="F1" t="str">
-        <v>header_row_span</v>
-      </c>
-      <c r="G1" t="str">
-        <v>auto_learned</v>
-      </c>
-      <c r="H1" t="str">
-        <v>tranche_count</v>
-      </c>
-      <c r="I1" t="str">
-        <v>has_grouping_rows</v>
-      </c>
-      <c r="J1" t="str">
-        <v>has_color_flags</v>
-      </c>
-      <c r="K1" t="str">
-        <v>summary_rows_above_header</v>
-      </c>
-      <c r="L1" t="str">
-        <v>summary_row_range</v>
-      </c>
-      <c r="M1" t="str">
-        <v>detect_keys</v>
-      </c>
-      <c r="N1" t="str">
-        <v>auto_discover_tabs</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>aep-vii</v>
-      </c>
-      <c r="B2" t="str">
-        <v>JP Morgan</v>
-      </c>
-      <c r="C2" t="str">
-        <v>A</v>
-      </c>
-      <c r="D2" t="str">
-        <v>BB</v>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
       </c>
       <c r="E2">
         <v>10</v>
@@ -482,59 +676,65 @@
       <c r="K2">
         <v>7</v>
       </c>
-      <c r="L2" t="str">
-        <v>3-9</v>
-      </c>
-      <c r="M2" t="str">
-        <v/>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>19</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
-  </ignoredErrors>
+  <printOptions/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  </headerFooter>
+  <extLst/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{FDE00D51-2351-453E-9CC0-445155FC4740}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" defaultColWidth="7.75390625" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>tab_role</v>
-      </c>
-      <c r="B1" t="str">
-        <v>tab_sort</v>
-      </c>
-      <c r="C1" t="str">
-        <v>sheet_name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>header_row_index</v>
-      </c>
-      <c r="E1" t="str">
-        <v>header_row_span</v>
-      </c>
-      <c r="F1" t="str">
-        <v>skip_row_keywords</v>
-      </c>
-      <c r="G1" t="str">
-        <v>expected_source_headers_json</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>LP_GRID</v>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" t="s">
+        <v>24</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="str">
-        <v>BB</v>
+      <c r="C2" t="s">
+        <v>17</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -542,344 +742,379 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" t="str">
-        <v>Total,Subtotal,Sub-Total,Grand Total,Sum,Net Total</v>
-      </c>
-      <c r="G2" t="str">
-        <v>["Investor","Moody's","S&amp;P","Net Worth","Total Commitment","Funded Commitment","Unfunded Commitment","% Total Unfunded Commitment","Concentration Limit","Excess Concentration","Eligible Unfunded Commitment","Advance Rate"]</v>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
-  </ignoredErrors>
+  <printOptions/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  </headerFooter>
+  <extLst/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{70B27296-A7DE-4649-BE81-1437F1291A2A}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" defaultColWidth="7.75390625" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="11.125" customWidth="1"/>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="3" max="3" width="28.625" customWidth="1"/>
+    <col min="4" max="4" width="26.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>tab_role</v>
-      </c>
-      <c r="B1" t="str">
-        <v>group_sort</v>
-      </c>
-      <c r="C1" t="str">
-        <v>header_text</v>
-      </c>
-      <c r="D1" t="str">
-        <v>classification</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>LP_GRID</v>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" t="s">
+        <v>24</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="str">
-        <v>Rated Included Investors</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Rated Included</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>LP_GRID</v>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="s">
+        <v>24</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="str">
-        <v>Non-Rated Included Investors</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Non-Rated Included</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>LP_GRID</v>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="s">
+        <v>24</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="str">
-        <v>Designated Investors</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Designated Institutional</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>LP_GRID</v>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="s">
+        <v>24</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" t="str">
-        <v>Excluded Investors</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Ineligible Investors</v>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
-  </ignoredErrors>
+  <printOptions/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  </headerFooter>
+  <extLst/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{07CBD058-C08E-47AE-8E14-4FF33B3E5643}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" defaultColWidth="7.75390625" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>tab_role</v>
-      </c>
-      <c r="B1" t="str">
-        <v>column_sort</v>
-      </c>
-      <c r="C1" t="str">
-        <v>source_header</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>LP_GRID</v>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" t="s">
+        <v>24</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="str">
-        <v>Investor</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>LP_GRID</v>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="s">
+        <v>24</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="str">
-        <v>Moody's</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>LP_GRID</v>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" t="s">
+        <v>24</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="str">
-        <v>S&amp;P</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>LP_GRID</v>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="s">
+        <v>24</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" t="str">
-        <v>Net Worth</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>LP_GRID</v>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="s">
+        <v>24</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" t="str">
-        <v>Total Commitment</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>LP_GRID</v>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="s">
+        <v>24</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" t="str">
-        <v>Funded Commitment</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>LP_GRID</v>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="s">
+        <v>24</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" t="str">
-        <v>Unfunded Commitment</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>LP_GRID</v>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="s">
+        <v>24</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" t="str">
-        <v>% Total Unfunded Commitment</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>LP_GRID</v>
+      <c r="C9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="s">
+        <v>24</v>
       </c>
       <c r="B10">
         <v>9</v>
       </c>
-      <c r="C10" t="str">
-        <v>Concentration Limit</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>LP_GRID</v>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="s">
+        <v>24</v>
       </c>
       <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11" t="str">
-        <v>Excess Concentration</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>LP_GRID</v>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="s">
+        <v>24</v>
       </c>
       <c r="B12">
         <v>11</v>
       </c>
-      <c r="C12" t="str">
-        <v>Eligible Unfunded Commitment</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>LP_GRID</v>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="s">
+        <v>24</v>
       </c>
       <c r="B13">
         <v>12</v>
       </c>
-      <c r="C13" t="str">
-        <v>Advance Rate</v>
+      <c r="C13" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
-  </ignoredErrors>
+  <printOptions/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  </headerFooter>
+  <extLst/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{0ACBD95A-864B-46B2-8B7F-F84ED87FF0F4}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" defaultColWidth="7.75390625" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>legend_sort</v>
-      </c>
-      <c r="B1" t="str">
-        <v>style</v>
-      </c>
-      <c r="C1" t="str">
-        <v>meaning</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Green shading</v>
-      </c>
-      <c r="C2" t="str">
-        <v>LP new to the BB, NOT via LP Transfer</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>Yellow shading</v>
-      </c>
-      <c r="C3" t="str">
-        <v>LP new to the BB via LP Transfer</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>Blue text</v>
-      </c>
-      <c r="C4" t="str">
-        <v>LP with a change in Commitment Amount</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>Underlined text</v>
-      </c>
-      <c r="C5" t="str">
-        <v>LP with a change in Category</v>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
-  </ignoredErrors>
+  <printOptions/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  </headerFooter>
+  <extLst/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{C1C58C5C-B2D8-4FA0-A764-36F1321657AD}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" defaultColWidth="7.75390625" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>note_sort</v>
-      </c>
-      <c r="B1" t="str">
-        <v>note</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Cell formatting encodes LP-level deltas — capture during extraction, not just the cell value.</v>
+      <c r="B2" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
-  </ignoredErrors>
+  <printOptions/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
+  </headerFooter>
+  <extLst/>
 </worksheet>
 </file>